--- a/data/analysis/educational_profiles.xlsx
+++ b/data/analysis/educational_profiles.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>Candidate 01_MUHAMMAD_SALMAN holds a PhD in Electrical Engineering from International Islamic University, Islamabad. They have a consistent progression in their specialization, with a minor initial drift from Pre-Engineering to Electronics Engineering. Their performance trend is improving, with a strong performance in their PhD.</t>
         </is>
       </c>
     </row>

--- a/data/analysis/educational_profiles.xlsx
+++ b/data/analysis/educational_profiles.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,7 +539,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Candidate 01_MUHAMMAD_SALMAN holds a PhD in Electrical Engineering from International Islamic University, Islamabad, with a normalized mark of 83.2%. He has a consistent progression in his specialization, starting from Pre-Engineering, then Electronics, and finally Electrical Engineering. His educational background is marked by improving performance and no significant gaps.</t>
+          <t>Candidate 01_MUHAMMAD_SALMAN holds a PhD in Electrical Engineering from International Islamic University, Islamabad, with a performance trend of improving. They have a consistent progression in their specialization, Electronics to Communication Systems, with no significant gaps in their education. Their highest degree is a PhD, and they have a strong academic record with marks above 75% in their PG and PhD degrees.</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Candidate 02_MUHAMMAD_SHAHWAZ holds a Master's degree in Engineering from NED UET Karachi, with a normalized mark of 74.2%. They have a consistent progression in their educational path, with no significant gaps detected. Their specialization has shown a minor drift from Engineering to Electronics.</t>
+          <t>Candidate 02_MUHAMMAD_SHAHWAZ holds a Master's degree in Engineering from NED UET Karachi, with a normalized mark of 74.2%. They have a consistent progression in their educational path, with a stable performance trend. Their specialization has shown a minor drift from Engineering to Electronics.</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>The candidate, 03_NASIR_ALI_SHAH, holds a PhD from Politecnico di Torino with a specialization in FPGA and GPU acceleration of complex computational algorithms. Their educational progression is consistent, with an improving performance trend. They have completed their education with no significant gaps.</t>
+          <t>Candidate 03_NASIR_ALI_SHAH holds a PhD from Politecnico di Torino with a specialization in FPGA and GPU acceleration of complex computational algorithms. The candidate has a consistent progression in education, with an improving performance trend. The educational background shows no significant gaps.</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Candidate 04_MUHAMMAD_FARRUKH holds a PhD in Electrical Engineering from Riphah International University, completed in 2024 with a normalized mark of 88.0%. The candidate has a consistent progression in their educational journey, with no significant gaps detected. Their specialization has shown a minor drift from Electronic Engineering to Digital Signal Processing.</t>
+          <t>The candidate holds a PhD in Electrical Engineering from Riphah International University, with a stable performance trend and no significant gaps in their educational progression. They have a consistent specialization in Electrical Engineering, with a minor drift from Electronic Engineering. Their academic performance is strong, with marks above 75% in their PG and PhD degrees.</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Candidate 06_FARMAN_ALI holds a PhD from Iqra National University, Peshawar, Pakistan, with a highest degree of PhD. The candidate has a consistent progression of degrees, with no significant gaps detected. The educational background includes degrees from unranked institutions, with marks ranging from 60.0% to 80.0%.</t>
+          <t>Candidate 06_FARMAN_ALI holds a PhD from Iqra National University, Peshawar, Pakistan, with a highest degree of PhD. The candidate has a consistent progression of education, with no significant gaps detected. The educational background shows a stable performance trend.</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Candidate 07_FIZA_MURTAZA holds a PhD in Computer Engineering from the University of Engineering and Technology Taxila, with a stable performance trend and no significant gaps in education. The candidate has a consistent specialization in Computer Engineering and its subfields. The educational background includes a BS in Electrical (Computer) Engineering from COMSATS Institute of Information Technology, Abbottabad, and an MS in Computer Engineering from the University of Engineering and Technology Taxila.</t>
+          <t>Candidate 07_FIZA_MURTAZA holds a PhD in Computer Engineering from the University of Engineering and Technology Taxila, with a stable performance trend and no significant gaps in education. The candidate has a consistent specialization in Computer Engineering and its subfields. The educational background is mostly from unranked institutions.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Candidate Tayyaba Gull holds a PhD in Power Electronics from Iqra National University, with a stable performance trend and no significant gaps in education. She has a consistent progression in her specialization, starting from Electrical Engineering and moving to Power Electronics. Her educational background includes a BSc in Electrical Engineering from the University of Engineering and Technology Peshawar, an MSc from Cecos University, and a PhD in Power Electronics from Iqra National University.</t>
+          <t>Candidate Tayyaba Gull holds a PhD in Power Electronics from Iqra National University, with a Master's degree from Cecos University and a Bachelor's degree in Electrical Engineering from the University of Engineering and Technology Peshawar. Her educational progression is consistent, with no significant gaps detected. She has maintained a stable performance trend throughout her academic career.</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Candidate 09_MUHAMMAD_ABUBAKAR holds a PhD from Jiangsu University, with a specialization in power electronics and power systems. They have a consistent progression in their education, with no significant gaps detected. Their performance trend is stable, with high marks in their MS and PhD degrees.</t>
+          <t>Candidate 09_MUHAMMAD_ABUBAKAR holds a PhD from Jiangsu University, with a consistent progression in specialization from Electronics Engineering to Power Electronics and Power Systems. The candidate has achieved high marks in all degrees, with the highest being 93.8% in the MS from International Islamic University. There are no significant gaps in the educational record.</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Candidate 10_MUHAMMAD_EHATISHAM holds a PhD in Computer Engineering from the University of Engineering and Technology, Taxila. Their academic progression is consistent, with a stable performance trend. They have a specialization in Computer Science and related fields, with some minor drift in their research focus.</t>
+          <t>Candidate 10_MUHAMMAD_EHATISHAM holds a PhD in Computer Engineering from the University of Engineering and Technology, Taxila, with a consistent progression in specialization. The candidate has achieved high marks in all degrees, with some minor specialization drift. The educational background is mostly from unranked institutions, but with no significant gaps detected.</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Candidate 11_WAQAS_AMIN holds a PhD in Electrical Energy Policy, Energy Trading, Smart Grid Technology from the University of Electronic Science and Technology. They have a consistent progression in their specialization, with a clear focus on Electrical Engineering. Their performance trend is improving, with a strong overall academic record.</t>
+          <t>Candidate 11_WAQAS_AMIN holds a PhD in Electrical Energy Policy, Energy Trading, Smart Grid Technology from the University of Electronic Science and Technology. They have a consistent progression in their educational specialization, with a clear focus on Electrical Engineering. Their performance trend has been improving throughout their academic career.</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Candidate 12_SYED_TAMOORULHASSAN holds a PhD in Communication Engineering from the University of Oulu, with a Master's in Communication Systems Engineering from Linkoping University. They have a Bachelor's in Telecommunication Engineering from the National University of Computer and Emerging Sciences. Their educational progression is consistent, with no significant gaps detected.</t>
+          <t>Candidate 12_SYED_TAMOORULHASSAN holds a PhD in Communication Engineering from the University of Oulu, with a Master's degree in Communication Systems Engineering from Linkoping University. They have a Bachelor's degree in Telecommunication Engineering from the National University of Computer and Emerging Sciences. Their educational progression is consistent, with no significant gaps detected.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Candidate 13_MANZOOR_ELLAHI holds a PhD in Electrical Engineering from The University of Lahore, with a consistent progression in specialization. They have achieved strong marks throughout their academic career, with a highest percentage of 90.5% in their PhD. The candidate has no significant gaps in their educational background.</t>
+          <t>Candidate 13_MANZOOR_ELLAHI holds a PhD in Electrical Engineering from The University of Lahore, with a consistent progression of degrees in the same field. The candidate's performance trend is improving, with no significant gaps in education. The PhD degree is from a recognized institution, with a high percentage of 90.5%.</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Candidate 14_SAROSH_TAHIR holds a PhD in Computer and Control Engineering from POLITECNICO DI TORINO, with a background in Electronics Engineering from COMSATS. The candidate's educational progression is not consistent, with a specialization drift from Pre-Eng to Communication and then to Next Generation Optical Networks. The candidate has no significant gaps in their educational history.</t>
+          <t>Candidate 14_SAROSH_TAHIR holds a PhD in Computer and Control Engineering from POLITECNICO DI TORINO, with a background in Electronics Engineering from COMSATS. The candidate's educational progression is not consistent, with a specialization drift from Pre-Eng to Communication and then to Next Generation Optical Networks. The candidate's performance trend is stable, with no significant gaps detected in their educational history.</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Candidate 15_M_USMAN_ABBASI holds a PhD in Electrical Engineering from National University of Computer and Emerging Sciences - FAST, with a normalized mark of 89.0%. They have a consistent progression in their educational journey, with no significant gaps detected. Their specialization in Electrical Engineering has shown a minor overlap with Biomedical Signal Processing.</t>
+          <t>Candidate 15_M_USMAN_ABBASI holds a PhD in Electrical Engineering from National University of Computer and Emerging Sciences - FAST, with a specialization in Biomedical Signal Processing. The candidate has a consistent progression in their educational journey, with no significant gaps detected. Their performance trend has been improving throughout their academic career.</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Candidate 16_MUZZAMIL_GHAFFAR holds a PhD from Air University, with a consistent progression of degrees from BSc to MS to PhD. The candidate's performance trend is improving, with marks ranging from 76% to 93.5%. There are no significant gaps in their educational history.</t>
+          <t>Candidate 16_MUZZAMIL_GHAFFAR holds a PhD from Air University, with a consistent progression of higher education degrees, including a BSc and an MS from the same institution. The candidate's performance has shown an improving trend throughout their academic career. No significant gaps in education were detected.</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Candidate 18_MUHAMMAD_AMJAD holds a PhD from POLITEHNICA Bucharest with a performance of 95.0%. They have a consistent progression in their educational journey, with a trend of improving performance. Their specialization has shown a minor drift from Pre Engineering to Electrical (Telecommunication) Engineeri and then to Information and Communication Systems and finally to Electronics Telecommunication Technology.</t>
+          <t>Candidate 18_MUHAMMAD_AMJAD holds a PhD from POLITEHNICA Bucharest with a performance of 95.0%. They have a consistent progression in their education, with a trend of improving performance. Their specialization has shown a minor drift from Pre Engineering to Electrical (Telecommunication) Engineeri, and then to Information and Communication Systems, and finally to Electronics Telecommunication Technology.</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Candidate 19_ASIM_MASOOD holds a PhD in Information and Communication Engineering from the University of Science and Technology of China, with a performance trend of improving. They have a consistent progression in their degrees, with a specialization drift of 0.08. Their educational background includes a Bachelor's in Electrical Engineering from NUST and a Master's in Microelectronic System and Telecommunication Engineering from the University of Liverpool.</t>
+          <t>Candidate 19_ASIM_MASOOD holds a PhD in Information and Communication Engineering from the University of Science and Technology of China, with a performance trend of improving. They have a consistent progression in their degrees, with a minor specialization drift. Their educational background includes a Bachelor's in Electrical Engineering from NUST and a Master's in Microelectronic System and Telecommunication Engineering from the University of Liverpool.</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Candidate 20_SYED_FASIH_ALI holds a PhD in Electrical Engineering from Lahore University of Management Science, with a consistent progression in specialization and no significant gaps in education. The candidate has achieved high marks in their academic pursuits, including a 97.0% in their UG degree and an 86.8% in their PG degree. Their educational background is marked by a consistent improvement in ranking, with their PhD institution ranked 801 by THE and 591 by QS.</t>
+          <t>Candidate 20_SYED_FASIH_ALI holds a PhD in Electrical Engineering from Lahore University of Management Science, with a previous Master's degree in Electrical Engineering from National University of Science and Technology. The candidate's undergraduate degree is in Computer Engineering from Bahauddin Zikriya University. The educational progression is consistent, with no significant gaps detected.</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,59 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Candidate 21_SAMAN_FATIMA holds a PhD from University Paris Saclay (CentraleSupelec) with a THE ranking of 83 and a QS ranking of 121. They have a consistent progression in their specialization from Pre-Engineering to Microelectronics - Analog IC Design. Their educational performance has been stable throughout their academic journey.</t>
+          <t>Candidate 21_SAMAN_FATIMA holds a PhD from University Paris Saclay (CentraleSupelec), a Master's degree from the same institution, and a B.Sc. from Islamia University of Bahawalpur. Their academic progression is consistent, with a stable performance trend. They have undergone specialization drifts, but with no overlap between fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22_ZEESHAN</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="C23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>improving</t>
+        </is>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>[{'from_degree': 'Pre Engineering', 'to_degree': 'Telecommunication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Telecommunication', 'to_degree': 'Machine Learning', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Machine Learning', 'to_degree': 'Informatics', 'overlap_score': 0.0, 'flagged': True}]</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Candidate 22_ZEESHAN holds a PhD from the Free University of Bolzano, a Master's degree from Chongqing University, and a dual undergraduate degree from The University of Lancaster and COMSATS. The candidate's educational progression is consistent, with an improving performance trend. No significant gaps were detected in their educational background.</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z112"/>
+  <dimension ref="A1:Z117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13163,6 +13215,498 @@
         <v>100</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>22_ZEESHAN</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SSC</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Matric</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Science group</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Faisalabad</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>83.6</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>83.6</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SSC</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>83.6</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="X113" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>Government College University Faisalabad</t>
+        </is>
+      </c>
+      <c r="Z113" t="n">
+        <v>83.33333333333334</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>22_ZEESHAN</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>HSSC</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>FSc</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Pre Engineering</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Superior College</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>HSSC</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="X114" t="n">
+        <v>74</v>
+      </c>
+      <c r="Y114" t="inlineStr"/>
+      <c r="Z114" t="n">
+        <v>53.33333333333334</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>22_ZEESHAN</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Electrical (Telecom) Engineering</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>The University of Lancaster- COMSATS Dual degree</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>79.23</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>79.23</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>79.23</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="X115" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>22_ZEESHAN</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Electronics and Communication</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Chongqing University</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="n">
+        <v>601</v>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>601-800</t>
+        </is>
+      </c>
+      <c r="R116" t="n">
+        <v>471</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>471-480</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="X116" t="n">
+        <v>86</v>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>Chongqing University</t>
+        </is>
+      </c>
+      <c r="Z116" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>22_ZEESHAN</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Advanced System Engineering</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Informatics</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Free University of Bolzano</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="X117" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>University of Lahore</t>
+        </is>
+      </c>
+      <c r="Z117" t="n">
+        <v>82.60869565217391</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/analysis/educational_profiles.xlsx
+++ b/data/analysis/educational_profiles.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>Muhammad Salman holds a PhD in Electrical Engineering from the International Islamic University, Islamabad, with a strong academic record and consistent specialization. His academic performance shows an improving trend, with no significant gaps detected in his educational history. He has a strong foundation in Electronics Engineering, with a progression from UG to PG and PhD in related fields.</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>The candidate, 03_NASIR_ALI_SHAH, holds a PhD degree from Politecnico di Torino with a perfect score of 100.0%. Their educational progression is consistent, and their performance trend is improving. The candidate's specialization has shown some drift, but they have maintained a strong academic record with no significant gaps detected in their educational history.</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>The candidate, 09_MUHAMMAD_ABUBAKAR, holds a PhD degree from Jiangsu University with a strong academic performance throughout their educational journey. They have a consistent progression in their field of study with a specialization in power electronics and power systems, which has a minor drift from their initial field of electronics engineering. The candidate's academic performance shows a stable trend with no significant gaps detected in their educational history.</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>The candidate holds a PhD in Electrical Energy Policy, Energy Trading, and Smart Grid Technology from the University of Electronic Science and Technology, with a strong academic performance of 90.0%. Their educational progression is consistent, and their performance trend is improving. The candidate's highest degree is a PhD from a ranked university, with no significant educational gaps detected.</t>
         </is>
       </c>
     </row>
@@ -748,14 +748,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>The candidate, 13_MANZOOR_ELLAHI, holds a PhD in Electrical Engineering from The University of Lahore with a strong academic performance, achieving 90.5% in their PhD program. Their educational progression is consistent, with a highest degree of PhD and an improving performance trend. The candidate's specialization has evolved over time, but their overall academic background is robust.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15_M_USMAN_ABBASI</t>
+          <t>16_MUZZAMIL_GHAFFAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -772,13 +772,9 @@
         </is>
       </c>
       <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>[{'from_degree': 'Electrical Engineering', 'to_degree': 'Biomedical Signal Processing', 'overlap_score': 0.0, 'flagged': True}]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>0</v>
       </c>
@@ -800,14 +796,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>The candidate, Muzzamil Ghaffar, holds a PhD degree from Air University with a high percentage of 93.5%. Their educational progression is consistent, with no significant gaps detected, and their performance trend is improving. They have demonstrated specialization consistency throughout their academic career.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16_MUZZAMIL_GHAFFAR</t>
+          <t>17_SUHAIL_ASGHAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -824,9 +820,13 @@
         </is>
       </c>
       <c r="E8" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electronics', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electronics', 'to_degree': 'Telecommunication Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
+        </is>
+      </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
@@ -848,14 +848,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>Suhail Asghar holds a PhD in Electrical Engineering from Universiti Tun Hussein Onn Malaysia, with a consistent progression and improving performance trend. His academic background demonstrates a strong foundation, with no significant gaps detected in his educational history. He has consistently specialized in fields related to electrical engineering, with high marks throughout his academic career.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17_SUHAIL_ASGHAR</t>
+          <t>18_MUHAMMAD_AMJAD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electronics', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electronics', 'to_degree': 'Telecommunication Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre Engineering', 'to_degree': 'Electrical (Telecommunication) Engineering', 'overlap_score': 0.25, 'flagged': True}, {'from_degree': 'Electrical (Telecommunication) Engineering', 'to_degree': 'Information and Communication Systems', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Information and Communication Systems', 'to_degree': 'Electronics Telecommunication Technology', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -900,14 +900,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>The candidate has a PhD from POLITEHNICA Bucharest with a high grade of 95.0%. Their educational progression is consistent, and their performance trend is improving. The candidate has a strong academic background with no significant gaps detected in their education.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18_MUHAMMAD_AMJAD</t>
+          <t>19_ASIM_MASOOD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre Engineering', 'to_degree': 'Electrical (Telecommunication) Engineering', 'overlap_score': 0.25, 'flagged': True}, {'from_degree': 'Electrical (Telecommunication) Engineering', 'to_degree': 'Information and Communication Systems', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Information and Communication Systems', 'to_degree': 'Electronics Telecommunication Technology', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electronics, Signal Processing', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Microelectronic System, Telecommunication, Signal Processing', 'to_degree': 'Machine Learning, Artificial Intelligence, Speech Processing, Natural Language P', 'overlap_score': 0.08, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -952,14 +952,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>Asim Masood holds a PhD in Information and Communication Engineering from the University of Science and Technology of China. His educational progression is consistent, with a highest degree of PhD and an improving performance trend. He has no significant educational gaps detected, and his specialization has evolved from pre-engineering to electronics and signal processing, and then to machine learning and artificial intelligence. His academic achievements and consistent progression justify his strong educational strength.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19_ASIM_MASOOD</t>
+          <t>22_ZEESHAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electronics, Signal Processing', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Microelectronic System, Telecommunication, Signal Processing', 'to_degree': 'Machine Learning, Artificial Intelligence, Speech Processing, Natural Language P', 'overlap_score': 0.08, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre Engineering', 'to_degree': 'Telecommunication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Telecommunication', 'to_degree': 'Machine Learning', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Machine Learning', 'to_degree': 'Informatics', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1004,14 +1004,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>Zeeshan has a PhD in Advanced System Engineering from the Free University of Bolzano, with a consistent progression in their educational background and an improving performance trend. They have a strong academic record, with high marks in their degrees, including 100% in their PhD. There are no significant gaps detected in their educational history, and their specialization has evolved from pre-engineering to informatics with some overlap.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20_SYED_FASIH_ALI</t>
+          <t>23_WAQAS_TARIQ_TOOR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>declining</t>
+          <t>improving</t>
         </is>
       </c>
       <c r="E12" t="b">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Computer Engineering', 'to_degree': 'Telecommunication and Networks', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Telecommunication and Networks', 'to_degree': 'Wireless Communication', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre Engineering', 'to_degree': 'Electronics and Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electronics and Communication', 'to_degree': 'Wireless Communication', 'overlap_score': 0.25, 'flagged': True}, {'from_degree': 'Wireless Communication', 'to_degree': 'Algorithm development for congestion control in IoT', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is declining.</t>
+          <t>The candidate, 23_WAQAS_TARIQ_TOOR, holds a PhD in Electronics and Communication Engineering from Hanyang University, with a consistent progression in their educational background. Their performance trend shows improvement, and there are no significant educational gaps detected. The candidate's specialization has drifted over time, but their highest degree is from a ranked university, supporting their strong educational profile.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22_ZEESHAN</t>
+          <t>24_AHMED_NAEEM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C13" t="b">
@@ -1084,11 +1084,11 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre Engineering', 'to_degree': 'Telecommunication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Telecommunication', 'to_degree': 'Machine Learning', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Machine Learning', 'to_degree': 'Informatics', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Majors in Communications', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Majors in Communications', 'to_degree': 'Machine Learning', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Machine Learning', 'to_degree': 'Wireless Communication Technologies and Cyber Systems and Cyber Security', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1108,14 +1108,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>Ahmed Naeem has a consistent educational progression with a highest degree of PG in Electrical-Electronics Engineering. His academic performance shows an improving trend, with strong marks in his postgraduate studies. He has no significant educational gaps, and his specialization, although with some drift, demonstrates a clear focus on electrical engineering and related fields.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>23_WAQAS_TARIQ_TOOR</t>
+          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>improving</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E14" t="b">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre Engineering', 'to_degree': 'Electronics and Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electronics and Communication', 'to_degree': 'Wireless Communication', 'overlap_score': 0.25, 'flagged': True}, {'from_degree': 'Wireless Communication', 'to_degree': 'Algorithm development for congestion control in IoT', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Security system', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Security system', 'to_degree': 'Communications and Networks', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communications and Networks', 'to_degree': 'Intelligent Systems and Control', 'overlap_score': 0.17, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>Muhammad Adeel Altaf holds a PhD in Electronic and Electrical Engineering from Kyungpook National University, with a strong academic performance of 95.0%. His educational progression is consistent, and his performance trend is stable. Although there is some specialization drift, his overall academic background and high marks in his PhD program justify a strong educational strength assessment.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>24_AHMED_NAEEM</t>
+          <t>28_IDRIS_KHAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1184,15 +1184,11 @@
         </is>
       </c>
       <c r="E15" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Majors in Communications', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Majors in Communications', 'to_degree': 'Machine Learning', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Machine Learning', 'to_degree': 'Wireless Communication Technologies and Cyber Systems and Cyber Security', 'overlap_score': 0.0, 'flagged': True}]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1212,14 +1208,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PG. Academic performance trend is improving.</t>
+          <t>The candidate, Idris Khan, has a consistent educational progression with a highest degree of Postgraduate in specialized fields related to Electrical Engineering. Their performance trend is improving, with no significant gaps detected in their educational history. They have achieved strong marks throughout their academic career, with percentages above 73% in all their degrees.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>27_SHAHEER</t>
+          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1240,7 +1236,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'pre engineering', 'to_degree': 'nan', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'nan', 'to_degree': 'Human Resource Management', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Human Resource Management', 'to_degree': 'POWER ELECTRONICS', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Electrical Engineering', 'to_degree': 'Power Systems', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1264,19 +1260,19 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>The candidate, Muhammad Sarmad Tariq, holds a PhD in Electrical Engineering from the University of North Carolina Charlotte, with a consistent specialization in Electrical Engineering and a strong academic performance throughout their educational journey. They have a highest degree of PhD and their progression is consistent, with an improving performance trend. The candidate's educational background is marked by high percentages, including 90.0% and 95.0% in their HSSC and PhD, respectively.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>28_IDRIS_KHAN</t>
+          <t>30_FAHD_SIKANDAR_KHAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="C17" t="b">
@@ -1288,9 +1284,13 @@
         </is>
       </c>
       <c r="E17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[{'from_degree': 'nan', 'to_degree': 'Electrical Engineering Computers', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electrical Engineering Computers', 'to_degree': 'Thin film fabrication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Thin film fabrication', 'to_degree': 'Interdisciplinary', 'overlap_score': 0.0, 'flagged': True}]</t>
+        </is>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
@@ -1312,14 +1312,14 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PG. Academic performance trend is improving.</t>
+          <t>Fahd Sikandar Khan holds a PhD in Doctor of Engineering from the University of Tokyo, with a strong academic record and consistent specialization progression. Their performance trend is improving, with high marks in their PhD and Masters degrees. There are no significant educational gaps detected in their profile, supporting their strong educational background.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
+          <t>31_USMAN_MASUD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Electrical Engineering', 'to_degree': 'Power Systems', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electrical and electronics engineering', 'overlap_score': 0.2, 'flagged': True}, {'from_degree': 'Electrical and electronics engineering', 'to_degree': 'Telecommunications Engineering', 'overlap_score': 0.2, 'flagged': True}, {'from_degree': 'Telecommunications Engineering', 'to_degree': 'Electrical and electronics engineering', 'overlap_score': 0.2, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1364,14 +1364,14 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>The candidate holds a PhD in Electrical Engineering from the University of Kassel, with a consistent specialization in the field. Their academic performance shows an improving trend, with high marks in their postgraduate and PhD studies. The candidate's educational background is strong, with no significant gaps detected in their academic history.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>30_FAHD_SIKANDAR_KHAN</t>
+          <t>32_QAISAR_HUSSAIN_ALVI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1380,21 +1380,17 @@
         </is>
       </c>
       <c r="C19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>improving</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E19" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[{'from_degree': 'nan', 'to_degree': 'Electrical Engineering Computers', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electrical Engineering Computers', 'to_degree': 'Thin film fabrication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Thin film fabrication', 'to_degree': 'Interdisciplinary', 'overlap_score': 0.0, 'flagged': True}]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>0</v>
       </c>
@@ -1416,14 +1412,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>Qaisar Hussain Alvi holds a PhD in Electrical Engineering from UET, Taxila, with a strong academic record, including 79.0% in PhD, 85.2% in PG, 76.1% in UG, and 74.8% in HSSC. The candidate's performance trend is stable, and no significant educational gaps were detected. Although the progression is not consistent, the overall academic performance justifies the strength label.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>31_USMAN_MASUD</t>
+          <t>34_SHAHZAD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1436,7 +1432,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>improving</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E20" t="b">
@@ -1444,7 +1440,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electrical and electronics engineering', 'overlap_score': 0.2, 'flagged': True}, {'from_degree': 'Electrical and electronics engineering', 'to_degree': 'Telecommunications Engineering', 'overlap_score': 0.2, 'flagged': True}, {'from_degree': 'Telecommunications Engineering', 'to_degree': 'Electrical and electronics engineering', 'overlap_score': 0.2, 'flagged': True}]</t>
+          <t>[{'from_degree': 'nan', 'to_degree': 'Computer Architecture, Computer Networks', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1468,14 +1464,14 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>The candidate has a PhD in Intelligent Mechatronics Engineering from Sejong University, with a consistent progression in their educational background. They have a strong academic record, with marks above 75% in their undergraduate and postgraduate degrees. The candidate's specialization has drifted from their initial field, but their performance trend has remained stable. They have no significant educational gaps in their profile.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>32_QAISAR_HUSSAIN_ALVI</t>
+          <t>37_SANIA_GUL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1484,11 +1480,11 @@
         </is>
       </c>
       <c r="C21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>improving</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -1516,14 +1512,14 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>Sania Gul has a PhD in Electrical Engineering from UET Peshawar with a high percentage of 98.8%. Her educational progression is consistent, with a specialization in Electrical Engineering throughout her degrees. She has shown an improving performance trend, with no significant gaps detected in her educational history.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>33_QAMAR_ABBAS</t>
+          <t>39_MUHAMMAD_SAQIB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1532,21 +1528,17 @@
         </is>
       </c>
       <c r="C22" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="E22" t="b">
         <v>0</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>declining</t>
-        </is>
-      </c>
-      <c r="E22" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>[{'from_degree': 'Internet of thing', 'to_degree': 'Computer Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
         <v>0</v>
       </c>
@@ -1568,19 +1560,19 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is declining.</t>
+          <t>Muhammad Saqib has completed his educational journey with a PhD from Jeju National University, maintaining a consistent specialization and strong academic performance throughout. His highest degree is a PhD, and his academic progression is consistent with no significant gaps detected. He has demonstrated a stable performance trend, with no specialization drift, and has achieved high marks in all his degrees.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>34_SHAHZAD</t>
+          <t>02_MUHAMMAD_SHAHWAZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C23" t="b">
@@ -1596,7 +1588,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'nan', 'to_degree': 'Computer Architecture, Computer Networks', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'ENGINEERING', 'to_degree': 'ELECTRONICS', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1610,24 +1602,24 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>Muhammad Shahwaz has a Master's degree in Engineering from NED UET Karachi with a consistent specialization in Engineering and Electronics. His academic performance has been stable, with a highest score of 77.0% in his SSC and an average of 74.2% in his Master's degree. He has no significant gaps in his educational history. His highest degree is a Postgraduate degree in Engineering.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>36_SAMANA_BATOOL</t>
+          <t>04_MUHAMMAD_FARRUKH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1636,11 +1628,11 @@
         </is>
       </c>
       <c r="C24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>declining</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E24" t="b">
@@ -1648,7 +1640,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Artificial Intelligence in medical domain', 'to_degree': 'Computer Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Electronic Engineering', 'to_degree': 'Digital Signal Processing', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1662,24 +1654,24 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is declining.</t>
+          <t>Muhammad Farrukh has a PhD in Electrical Engineering from Riphah International University with a strong mark of 88.0%. He has a consistent progression in his educational background, with a stable performance trend. However, his university is not ranked, which affects his overall educational strength. His specialization has drifted from Electronic Engineering to Electrical Engineering, but this does not seem to have negatively impacted his academic performance.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>37_SANIA_GUL</t>
+          <t>05_MUHAMMAD_MAJID</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1692,13 +1684,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>improving</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E25" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>[{'from_degree': 'PRE ENGINEERING', 'to_degree': 'ELECTRONICS', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'ELECTRONICS', 'to_degree': 'WIRELESS COMMUNICATION', 'overlap_score': 0.0, 'flagged': True}]</t>
+        </is>
+      </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
@@ -1710,24 +1706,24 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>Muhammad Majid holds a PhD in Electrical Engineering from the Institute of Space Technology with a strong mark of 90.0%. His educational progression is consistent, with a stable performance trend and no significant gaps detected. However, his institutions are not ranked, which prevents his profile from being classified as strong.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>38_MUHAMMAD_MUSADIQ</t>
+          <t>06_FARMAN_ALI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1736,11 +1732,11 @@
         </is>
       </c>
       <c r="C26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>declining</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E26" t="b">
@@ -1758,24 +1754,24 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is declining.</t>
+          <t>Farman Ali holds a PhD degree from Iqra National University, Peshawar, Pakistan, with a consistent progression and stable performance trend. The candidate's highest degree is a PhD, with no significant gaps detected in their educational history. The institutions attended are not ranked, which is a factor in the moderate educational strength assessment.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>39_MUHAMMAD_SAQIB</t>
+          <t>07_FIZA_MURTAZA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1792,9 +1788,13 @@
         </is>
       </c>
       <c r="E27" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>[{'from_degree': 'Computer Engineering', 'to_degree': 'Signal and Image Processing', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Signal and Image Processing', 'to_degree': 'Computer Vision, Temporal Human Action Detection', 'overlap_score': 0.0, 'flagged': True}]</t>
+        </is>
+      </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
@@ -1806,24 +1806,24 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>The candidate, 07_FIZA_MURTAZA, holds a PhD in Computer Engineering from the University of Engineering and Technology Taxila, with a consistent progression and stable performance trend. Their highest degree is a PhD, and they have no significant educational gaps. However, the institutions they attended are not ranked highly, which contributes to their moderate educational strength.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>41_MUHAMMAD_AQEEL</t>
+          <t>08_TAYYABA_GULL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>improving</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Phy, Math, Computer', 'to_degree': 'Telecommunication Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Electrical Engr', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communication', 'to_degree': 'Power Electronics', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1858,24 +1858,24 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>The candidate, 08_TAYYABA_GULL, has a PhD in Power Electronics from Iqra National University with a strong mark of 89.5%. Their educational progression is consistent, with a stable performance trend. However, there is a specialization drift from Electrical Engineering to Power Electronics, which may be a factor in the assessment. The candidate's institutions are not ranked, contributing to the moderate educational strength label.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>43_AMMARA_NASIM</t>
+          <t>10_MUHAMMAD_EHATISHAM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1884,11 +1884,11 @@
         </is>
       </c>
       <c r="C29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>insufficient data</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E29" t="b">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'nan', 'to_degree': 'Computer Vision, AI, Deep Learning', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Computer Science', 'to_degree': 'nan', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'nan', 'to_degree': 'Signal and Image Processing', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Signal and Image Processing', 'to_degree': 'Artificial Intelligence and Pervasive Computing', 'overlap_score': 0.12, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1910,29 +1910,29 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD.</t>
+          <t>The candidate has a PhD in Computer Engineering from the University of Engineering and Technology, Taxila, with a consistent specialization and strong marks throughout their academic career. They have also completed a course in Multimodal Data Processing and Machine Learning from the University of East London. The candidate's educational progression is consistent, and there are no significant gaps in their education. However, the universities they attended are not ranked, which affects their overall educational strength.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>02_MUHAMMAD_SHAHWAZ</t>
+          <t>12_SYED_TAMOORULHASSAN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="C30" t="b">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'ENGINEERING', 'to_degree': 'ELECTRONICS', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Telecommunication Engineering', 'to_degree': 'Communication Systems', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1972,14 +1972,14 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PG. Academic performance trend is stable.</t>
+          <t>The candidate has a PhD in Communication Engineering from the University of Oulu, with a consistent progression in their educational background. They have a strong performance trend, with stable marks throughout their academic career. The candidate's specialization has drifted from Telecommunication Engineering to Communication Systems, but they have achieved high marks in their PhD program.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>04_MUHAMMAD_FARRUKH</t>
+          <t>14_SAROSH_TAHIR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Electronic Engineering', 'to_degree': 'Digital Signal Processing', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre-Eng', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communication', 'to_degree': 'Next Generation Optical Networks', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Next Generation Optical Networks', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2024,14 +2024,14 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>The candidate holds a PhD in Computer and Control Engineering from Politecnico di Torino. Their educational progression is not consistent, with specialization drift observed across different degrees. The candidate's performance trend is stable, and no significant educational gaps were detected. They have a strong foundation in engineering, with degrees in Electronics Engineering and Telecommunication and Networking.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05_MUHAMMAD_MAJID</t>
+          <t>15_M_USMAN_ABBASI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>improving</t>
         </is>
       </c>
       <c r="E32" t="b">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'PRE ENGINEERING', 'to_degree': 'ELECTRONICS', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'ELECTRONICS', 'to_degree': 'WIRELESS COMMUNICATION', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Electrical Engineering', 'to_degree': 'Biomedical Signal Processing', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>The candidate has a PhD in Electrical Engineering from the National University of Computer and Emerging Sciences - FAST, with a consistent progression and improving performance trend. However, the specialization drift from Electrical Engineering to Biomedical Signal Processing indicates a minor drift. The candidate's academic background is solid, but the lack of ranking for most institutions attended is a factor in the assessment.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06_FARMAN_ALI</t>
+          <t>20_SYED_FASIH_ALI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2096,13 +2096,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>declining</t>
         </is>
       </c>
       <c r="E33" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>[{'from_degree': 'Computer Engineering', 'to_degree': 'Telecommunication and Networks', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Telecommunication and Networks', 'to_degree': 'Wireless Communication', 'overlap_score': 0.0, 'flagged': True}]</t>
+        </is>
+      </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
@@ -2119,19 +2123,19 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>The candidate, 20_SYED_FASIH_ALI, holds a PhD in Electrical Engineering from Lahore University of Management Science. Their educational progression is consistent, with a specialization that has drifted from Computer Engineering to Electrical Engineering. The candidate's performance trend is declining, which is a concern. Despite this, they have achieved strong marks in their undergraduate degree and a respectable mark in their PhD.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07_FIZA_MURTAZA</t>
+          <t>21_SAMAN_FATIMA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2152,7 +2156,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Computer Engineering', 'to_degree': 'Signal and Image Processing', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Signal and Image Processing', 'to_degree': 'Computer Vision, Temporal Human Action Detection', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electronics', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electronics', 'to_degree': 'E3A -M2 Integration circuits-systemes', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'E3A -M2 Integration circuits-systemes', 'to_degree': 'Microelectronics - Analog IC Design', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2176,14 +2180,14 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>Saman Fatima has completed her educational degrees consistently, with a highest degree of PhD from University Paris Saclay. Her performance trend has been stable, and there are no significant educational gaps detected. However, the universities for her earlier degrees are not ranked, which affects her overall educational strength.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08_TAYYABA_GULL</t>
+          <t>26_AAMINA_AKBAR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2204,7 +2208,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Electrical Engr', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communication', 'to_degree': 'Power Electronics', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Telecommunication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Telecommunication', 'to_degree': 'Wireless Communication, Convex Optimization', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2228,14 +2232,14 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>Aamina Akbar holds a PhD in Electrical Engineering with a specialization in Communication from the Institute of Space Technology. Her educational progression is consistent, and her performance trend is stable. She has a strong academic record, with high marks in her postgraduate and PhD studies, but her universities are not ranked in the top tiers, which is a factor in her moderate educational strength assessment.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10_MUHAMMAD_EHATISHAM</t>
+          <t>27_SHAHEER</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2248,7 +2252,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>improving</t>
         </is>
       </c>
       <c r="E36" t="b">
@@ -2256,7 +2260,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Computer Science', 'to_degree': 'nan', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'nan', 'to_degree': 'Signal and Image Processing', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Signal and Image Processing', 'to_degree': 'Artificial Intelligence and Pervasive Computing', 'overlap_score': 0.12, 'flagged': True}]</t>
+          <t>[{'from_degree': 'pre engineering', 'to_degree': 'nan', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'nan', 'to_degree': 'Human Resource Management', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Human Resource Management', 'to_degree': 'POWER ELECTRONICS', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2275,19 +2279,19 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>The candidate has a PhD degree from University Malaysia Pahang, with a consistent progression in their educational background. However, the institutions they attended are not ranked, and there are significant specialization drifts throughout their degrees. The candidate's performance trend is improving, and there are no significant educational gaps detected.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12_SYED_TAMOORULHASSAN</t>
+          <t>35_MATIULLAH_AHSAN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2308,7 +2312,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Telecommunication Engineering', 'to_degree': 'Communication Systems', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'nan', 'to_degree': 'Electrical Power System, High Voltage, Artificial Intelligence', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2332,14 +2336,14 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>The candidate, Matiullah Ahsan, holds a PhD in Electrical Engineering from Universiti Tun Hussein Onn Malaysia with a strong mark of 85.0%. Their educational progression is consistent, with a stable performance trend and no significant gaps detected. The candidate's specialization has drifted from an undefined area to Electrical Power System and High Voltage, with no overlap.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>14_SAROSH_TAHIR</t>
+          <t>36_SAMANA_BATOOL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2352,7 +2356,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>declining</t>
         </is>
       </c>
       <c r="E38" t="b">
@@ -2360,7 +2364,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre-Eng', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communication', 'to_degree': 'Next Generation Optical Networks', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Next Generation Optical Networks', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Artificial Intelligence in medical domain', 'to_degree': 'Computer Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2379,19 +2383,19 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>The candidate holds a PhD in Electrical Engineering from a ranked university, with a perfect score. However, their educational progression is inconsistent, and their performance trend is declining. The candidate's specialization has also drifted significantly, from Artificial Intelligence in the medical domain to Computer Engineering, with no overlap.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>21_SAMAN_FATIMA</t>
+          <t>38_MUHAMMAD_MUSADIQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2400,21 +2404,17 @@
         </is>
       </c>
       <c r="C39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>declining</t>
         </is>
       </c>
       <c r="E39" t="b">
-        <v>1</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electronics', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electronics', 'to_degree': 'E3A -M2 Integration circuits-systemes', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'E3A -M2 Integration circuits-systemes', 'to_degree': 'Microelectronics - Analog IC Design', 'overlap_score': 0.0, 'flagged': True}]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
         <v>0</v>
       </c>
@@ -2431,19 +2431,19 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>Muhammad Musadiq holds a PhD in Electrical Engineering from The Islamia University of Bahawalpur with a high percentage of 98.8%. However, the university is not ranked, and his performance trend shows a decline. He has a consistent specialization in Electrical Engineering throughout his degrees.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
+          <t>40_ABDUR_REHMAN</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Security system', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Security system', 'to_degree': 'Communications and Networks', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communications and Networks', 'to_degree': 'Intelligent Systems and Control', 'overlap_score': 0.17, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'nan', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'nan', 'to_degree': 'Design of Electric Machines', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2488,14 +2488,14 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>Abdur Rehman holds a PhD in Electrical Engineering from Kunsan National University, with a consistent specialization and stable performance trend. The candidate's academic progression is consistent, with no significant gaps detected in their educational history. Abdur Rehman's highest degree is a PhD, achieved with a strong mark of 85.8%, although the universities attended are not ranked.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>26_AAMINA_AKBAR</t>
+          <t>41_MUHAMMAD_AQEEL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>improving</t>
         </is>
       </c>
       <c r="E41" t="b">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Telecommunication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Telecommunication', 'to_degree': 'Wireless Communication, Convex Optimization', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Phy, Math, Computer', 'to_degree': 'Telecommunication Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2535,19 +2535,19 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>The candidate, Muhammad Aqeel, has a PhD degree from KFUEIT with a strong academic performance trend, achieving 83.5% in their PhD program. Their educational progression is consistent, with no significant gaps detected. However, the universities they attended are not ranked, which affects their overall educational strength. The candidate's specialization has drifted from Phy, Math, Computer to Telecommunication Engineering.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>35_MATIULLAH_AHSAN</t>
+          <t>42_SAQIB_JAMIL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>improving</t>
         </is>
       </c>
       <c r="E42" t="b">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'nan', 'to_degree': 'Electrical Power System, High Voltage, Artificial Intelligence', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'nan', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communication and Electronics', 'to_degree': 'Plasmonics', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2592,14 +2592,14 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>The candidate has a PhD in Electrical Engineering from Sarhad University Peshawar, with a consistent progression and improving performance trend. Their highest degree is a PhD, and they have no significant educational gaps. The candidate's specialization has drifted over time, but they have maintained a strong academic record, with their highest marks being 87.2% in their PG degree and 85.5% in their PhD. The candidate's academic background is notable, but the lack of ranking for their institutions is a factor in their moderate educational strength.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>40_ABDUR_REHMAN</t>
+          <t>43_AMMARA_NASIM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2608,11 +2608,11 @@
         </is>
       </c>
       <c r="C43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>insufficient data</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'nan', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'nan', 'to_degree': 'Design of Electric Machines', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'nan', 'to_degree': 'Computer Vision, AI, Deep Learning', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2639,19 +2639,19 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+          <t>The candidate, Ammara Nasim, holds a PhD in Computer Engineering from NUST, CEME, with a strong academic performance of 98.0%. However, their educational progression is not consistent, with a specialization drift from their initial field to Computer Vision, AI, and Deep Learning. The candidate's academic background is diverse, with degrees from multiple institutions, including NUST and UET Taxila.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>42_SAQIB_JAMIL</t>
+          <t>33_QAMAR_ABBAS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2660,11 +2660,11 @@
         </is>
       </c>
       <c r="C44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>improving</t>
+          <t>declining</t>
         </is>
       </c>
       <c r="E44" t="b">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'nan', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communication and Electronics', 'to_degree': 'Plasmonics', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Internet of thing', 'to_degree': 'Computer Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2686,17 +2686,17 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+          <t>The candidate, 33_QAMAR_ABBAS, holds a PhD from SEECS NUST with an 87.5% mark, but their educational profile shows a declining performance trend and specialization drift from Internet of Things to Computer Engineering. Their highest degree is a PhD, but the progression is not consistent. The candidate's performance has been declining over time, which raises concerns about their academic strength.</t>
         </is>
       </c>
     </row>

--- a/data/analysis/educational_profiles.xlsx
+++ b/data/analysis/educational_profiles.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,7 +540,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Muhammad Salman holds a PhD in Electrical Engineering from the International Islamic University, Islamabad, with a strong academic record and consistent specialization. His academic performance shows an improving trend, with no significant gaps detected in his educational history. He has a strong foundation in Electronics Engineering, with a progression from UG to PG and PhD in related fields.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>The candidate, 03_NASIR_ALI_SHAH, holds a PhD degree from Politecnico di Torino with a perfect score of 100.0%. Their educational progression is consistent, and their performance trend is improving. The candidate's specialization has shown some drift, but they have maintained a strong academic record with no significant gaps detected in their educational history.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>The candidate, 09_MUHAMMAD_ABUBAKAR, holds a PhD degree from Jiangsu University with a strong academic performance throughout their educational journey. They have a consistent progression in their field of study with a specialization in power electronics and power systems, which has a minor drift from their initial field of electronics engineering. The candidate's academic performance shows a stable trend with no significant gaps detected in their educational history.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>The candidate holds a PhD in Electrical Energy Policy, Energy Trading, and Smart Grid Technology from the University of Electronic Science and Technology, with a strong academic performance of 90.0%. Their educational progression is consistent, and their performance trend is improving. The candidate's highest degree is a PhD from a ranked university, with no significant educational gaps detected.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
@@ -748,14 +748,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>The candidate, 13_MANZOOR_ELLAHI, holds a PhD in Electrical Engineering from The University of Lahore with a strong academic performance, achieving 90.5% in their PhD program. Their educational progression is consistent, with a highest degree of PhD and an improving performance trend. The candidate's specialization has evolved over time, but their overall academic background is robust.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16_MUZZAMIL_GHAFFAR</t>
+          <t>15_M_USMAN_ABBASI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -772,9 +772,13 @@
         </is>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[{'from_degree': 'Electrical Engineering', 'to_degree': 'Biomedical Signal Processing', 'overlap_score': 0.0, 'flagged': True}]</t>
+        </is>
+      </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
@@ -796,14 +800,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>The candidate, Muzzamil Ghaffar, holds a PhD degree from Air University with a high percentage of 93.5%. Their educational progression is consistent, with no significant gaps detected, and their performance trend is improving. They have demonstrated specialization consistency throughout their academic career.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17_SUHAIL_ASGHAR</t>
+          <t>16_MUZZAMIL_GHAFFAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,13 +824,9 @@
         </is>
       </c>
       <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electronics', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electronics', 'to_degree': 'Telecommunication Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>0</v>
       </c>
@@ -848,14 +848,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Suhail Asghar holds a PhD in Electrical Engineering from Universiti Tun Hussein Onn Malaysia, with a consistent progression and improving performance trend. His academic background demonstrates a strong foundation, with no significant gaps detected in his educational history. He has consistently specialized in fields related to electrical engineering, with high marks throughout his academic career.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18_MUHAMMAD_AMJAD</t>
+          <t>17_SUHAIL_ASGHAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre Engineering', 'to_degree': 'Electrical (Telecommunication) Engineering', 'overlap_score': 0.25, 'flagged': True}, {'from_degree': 'Electrical (Telecommunication) Engineering', 'to_degree': 'Information and Communication Systems', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Information and Communication Systems', 'to_degree': 'Electronics Telecommunication Technology', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electronics', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electronics', 'to_degree': 'Telecommunication Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -900,14 +900,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>The candidate has a PhD from POLITEHNICA Bucharest with a high grade of 95.0%. Their educational progression is consistent, and their performance trend is improving. The candidate has a strong academic background with no significant gaps detected in their education.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19_ASIM_MASOOD</t>
+          <t>18_MUHAMMAD_AMJAD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electronics, Signal Processing', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Microelectronic System, Telecommunication, Signal Processing', 'to_degree': 'Machine Learning, Artificial Intelligence, Speech Processing, Natural Language P', 'overlap_score': 0.08, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre Engineering', 'to_degree': 'Electrical (Telecommunication) Engineering', 'overlap_score': 0.25, 'flagged': True}, {'from_degree': 'Electrical (Telecommunication) Engineering', 'to_degree': 'Information and Communication Systems', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Information and Communication Systems', 'to_degree': 'Electronics Telecommunication Technology', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -952,14 +952,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Asim Masood holds a PhD in Information and Communication Engineering from the University of Science and Technology of China. His educational progression is consistent, with a highest degree of PhD and an improving performance trend. He has no significant educational gaps detected, and his specialization has evolved from pre-engineering to electronics and signal processing, and then to machine learning and artificial intelligence. His academic achievements and consistent progression justify his strong educational strength.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22_ZEESHAN</t>
+          <t>19_ASIM_MASOOD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre Engineering', 'to_degree': 'Telecommunication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Telecommunication', 'to_degree': 'Machine Learning', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Machine Learning', 'to_degree': 'Informatics', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electronics, Signal Processing', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Microelectronic System, Telecommunication, Signal Processing', 'to_degree': 'Machine Learning, Artificial Intelligence, Speech Processing, Natural Language P', 'overlap_score': 0.08, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1004,14 +1004,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Zeeshan has a PhD in Advanced System Engineering from the Free University of Bolzano, with a consistent progression in their educational background and an improving performance trend. They have a strong academic record, with high marks in their degrees, including 100% in their PhD. There are no significant gaps detected in their educational history, and their specialization has evolved from pre-engineering to informatics with some overlap.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>23_WAQAS_TARIQ_TOOR</t>
+          <t>20_SYED_FASIH_ALI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>improving</t>
+          <t>declining</t>
         </is>
       </c>
       <c r="E12" t="b">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre Engineering', 'to_degree': 'Electronics and Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electronics and Communication', 'to_degree': 'Wireless Communication', 'overlap_score': 0.25, 'flagged': True}, {'from_degree': 'Wireless Communication', 'to_degree': 'Algorithm development for congestion control in IoT', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Computer Engineering', 'to_degree': 'Telecommunication and Networks', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Telecommunication and Networks', 'to_degree': 'Wireless Communication', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>The candidate, 23_WAQAS_TARIQ_TOOR, holds a PhD in Electronics and Communication Engineering from Hanyang University, with a consistent progression in their educational background. Their performance trend shows improvement, and there are no significant educational gaps detected. The candidate's specialization has drifted over time, but their highest degree is from a ranked university, supporting their strong educational profile.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is declining.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>24_AHMED_NAEEM</t>
+          <t>22_ZEESHAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="C13" t="b">
@@ -1084,11 +1084,11 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Majors in Communications', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Majors in Communications', 'to_degree': 'Machine Learning', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Machine Learning', 'to_degree': 'Wireless Communication Technologies and Cyber Systems and Cyber Security', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre Engineering', 'to_degree': 'Telecommunication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Telecommunication', 'to_degree': 'Machine Learning', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Machine Learning', 'to_degree': 'Informatics', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1108,14 +1108,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ahmed Naeem has a consistent educational progression with a highest degree of PG in Electrical-Electronics Engineering. His academic performance shows an improving trend, with strong marks in his postgraduate studies. He has no significant educational gaps, and his specialization, although with some drift, demonstrates a clear focus on electrical engineering and related fields.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
+          <t>23_WAQAS_TARIQ_TOOR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>improving</t>
         </is>
       </c>
       <c r="E14" t="b">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Security system', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Security system', 'to_degree': 'Communications and Networks', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communications and Networks', 'to_degree': 'Intelligent Systems and Control', 'overlap_score': 0.17, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre Engineering', 'to_degree': 'Electronics and Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electronics and Communication', 'to_degree': 'Wireless Communication', 'overlap_score': 0.25, 'flagged': True}, {'from_degree': 'Wireless Communication', 'to_degree': 'Algorithm development for congestion control in IoT', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Muhammad Adeel Altaf holds a PhD in Electronic and Electrical Engineering from Kyungpook National University, with a strong academic performance of 95.0%. His educational progression is consistent, and his performance trend is stable. Although there is some specialization drift, his overall academic background and high marks in his PhD program justify a strong educational strength assessment.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28_IDRIS_KHAN</t>
+          <t>24_AHMED_NAEEM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1184,11 +1184,15 @@
         </is>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Majors in Communications', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Majors in Communications', 'to_degree': 'Machine Learning', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Machine Learning', 'to_degree': 'Wireless Communication Technologies and Cyber Systems and Cyber Security', 'overlap_score': 0.0, 'flagged': True}]</t>
+        </is>
+      </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1208,14 +1212,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>The candidate, Idris Khan, has a consistent educational progression with a highest degree of Postgraduate in specialized fields related to Electrical Engineering. Their performance trend is improving, with no significant gaps detected in their educational history. They have achieved strong marks throughout their academic career, with percentages above 73% in all their degrees.</t>
+          <t>The candidate's highest qualification is PG. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
+          <t>27_SHAHEER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1236,7 +1240,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Electrical Engineering', 'to_degree': 'Power Systems', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'pre engineering', 'to_degree': 'nan', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'nan', 'to_degree': 'Human Resource Management', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Human Resource Management', 'to_degree': 'POWER ELECTRONICS', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1260,19 +1264,19 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>The candidate, Muhammad Sarmad Tariq, holds a PhD in Electrical Engineering from the University of North Carolina Charlotte, with a consistent specialization in Electrical Engineering and a strong academic performance throughout their educational journey. They have a highest degree of PhD and their progression is consistent, with an improving performance trend. The candidate's educational background is marked by high percentages, including 90.0% and 95.0% in their HSSC and PhD, respectively.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30_FAHD_SIKANDAR_KHAN</t>
+          <t>28_IDRIS_KHAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C17" t="b">
@@ -1284,13 +1288,9 @@
         </is>
       </c>
       <c r="E17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>[{'from_degree': 'nan', 'to_degree': 'Electrical Engineering Computers', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electrical Engineering Computers', 'to_degree': 'Thin film fabrication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Thin film fabrication', 'to_degree': 'Interdisciplinary', 'overlap_score': 0.0, 'flagged': True}]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>0</v>
       </c>
@@ -1312,14 +1312,14 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Fahd Sikandar Khan holds a PhD in Doctor of Engineering from the University of Tokyo, with a strong academic record and consistent specialization progression. Their performance trend is improving, with high marks in their PhD and Masters degrees. There are no significant educational gaps detected in their profile, supporting their strong educational background.</t>
+          <t>The candidate's highest qualification is PG. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>31_USMAN_MASUD</t>
+          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electrical and electronics engineering', 'overlap_score': 0.2, 'flagged': True}, {'from_degree': 'Electrical and electronics engineering', 'to_degree': 'Telecommunications Engineering', 'overlap_score': 0.2, 'flagged': True}, {'from_degree': 'Telecommunications Engineering', 'to_degree': 'Electrical and electronics engineering', 'overlap_score': 0.2, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Electrical Engineering', 'to_degree': 'Power Systems', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1364,14 +1364,14 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>The candidate holds a PhD in Electrical Engineering from the University of Kassel, with a consistent specialization in the field. Their academic performance shows an improving trend, with high marks in their postgraduate and PhD studies. The candidate's educational background is strong, with no significant gaps detected in their academic history.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>32_QAISAR_HUSSAIN_ALVI</t>
+          <t>30_FAHD_SIKANDAR_KHAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1380,17 +1380,21 @@
         </is>
       </c>
       <c r="C19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>improving</t>
         </is>
       </c>
       <c r="E19" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>[{'from_degree': 'nan', 'to_degree': 'Electrical Engineering Computers', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electrical Engineering Computers', 'to_degree': 'Thin film fabrication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Thin film fabrication', 'to_degree': 'Interdisciplinary', 'overlap_score': 0.0, 'flagged': True}]</t>
+        </is>
+      </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
@@ -1412,14 +1416,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Qaisar Hussain Alvi holds a PhD in Electrical Engineering from UET, Taxila, with a strong academic record, including 79.0% in PhD, 85.2% in PG, 76.1% in UG, and 74.8% in HSSC. The candidate's performance trend is stable, and no significant educational gaps were detected. Although the progression is not consistent, the overall academic performance justifies the strength label.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>34_SHAHZAD</t>
+          <t>31_USMAN_MASUD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1432,7 +1436,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>improving</t>
         </is>
       </c>
       <c r="E20" t="b">
@@ -1440,7 +1444,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'nan', 'to_degree': 'Computer Architecture, Computer Networks', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electrical and electronics engineering', 'overlap_score': 0.2, 'flagged': True}, {'from_degree': 'Electrical and electronics engineering', 'to_degree': 'Telecommunications Engineering', 'overlap_score': 0.2, 'flagged': True}, {'from_degree': 'Telecommunications Engineering', 'to_degree': 'Electrical and electronics engineering', 'overlap_score': 0.2, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1464,14 +1468,14 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>The candidate has a PhD in Intelligent Mechatronics Engineering from Sejong University, with a consistent progression in their educational background. They have a strong academic record, with marks above 75% in their undergraduate and postgraduate degrees. The candidate's specialization has drifted from their initial field, but their performance trend has remained stable. They have no significant educational gaps in their profile.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>37_SANIA_GUL</t>
+          <t>32_QAISAR_HUSSAIN_ALVI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1480,11 +1484,11 @@
         </is>
       </c>
       <c r="C21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>improving</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -1512,14 +1516,14 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sania Gul has a PhD in Electrical Engineering from UET Peshawar with a high percentage of 98.8%. Her educational progression is consistent, with a specialization in Electrical Engineering throughout her degrees. She has shown an improving performance trend, with no significant gaps detected in her educational history.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>39_MUHAMMAD_SAQIB</t>
+          <t>33_QAMAR_ABBAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1528,17 +1532,21 @@
         </is>
       </c>
       <c r="C22" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>declining</t>
+        </is>
+      </c>
+      <c r="E22" t="b">
         <v>1</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
-      <c r="E22" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>[{'from_degree': 'Internet of thing', 'to_degree': 'Computer Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
+        </is>
+      </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
@@ -1560,19 +1568,19 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Muhammad Saqib has completed his educational journey with a PhD from Jeju National University, maintaining a consistent specialization and strong academic performance throughout. His highest degree is a PhD, and his academic progression is consistent with no significant gaps detected. He has demonstrated a stable performance trend, with no specialization drift, and has achieved high marks in all his degrees.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is declining.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>02_MUHAMMAD_SHAHWAZ</t>
+          <t>34_SHAHZAD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="C23" t="b">
@@ -1588,7 +1596,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'ENGINEERING', 'to_degree': 'ELECTRONICS', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'nan', 'to_degree': 'Computer Architecture, Computer Networks', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1602,24 +1610,24 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Muhammad Shahwaz has a Master's degree in Engineering from NED UET Karachi with a consistent specialization in Engineering and Electronics. His academic performance has been stable, with a highest score of 77.0% in his SSC and an average of 74.2% in his Master's degree. He has no significant gaps in his educational history. His highest degree is a Postgraduate degree in Engineering.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04_MUHAMMAD_FARRUKH</t>
+          <t>36_SAMANA_BATOOL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1628,11 +1636,11 @@
         </is>
       </c>
       <c r="C24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>declining</t>
         </is>
       </c>
       <c r="E24" t="b">
@@ -1640,7 +1648,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Electronic Engineering', 'to_degree': 'Digital Signal Processing', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Artificial Intelligence in medical domain', 'to_degree': 'Computer Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1654,24 +1662,24 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Muhammad Farrukh has a PhD in Electrical Engineering from Riphah International University with a strong mark of 88.0%. He has a consistent progression in his educational background, with a stable performance trend. However, his university is not ranked, which affects his overall educational strength. His specialization has drifted from Electronic Engineering to Electrical Engineering, but this does not seem to have negatively impacted his academic performance.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is declining.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05_MUHAMMAD_MAJID</t>
+          <t>37_SANIA_GUL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1684,17 +1692,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>improving</t>
         </is>
       </c>
       <c r="E25" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>[{'from_degree': 'PRE ENGINEERING', 'to_degree': 'ELECTRONICS', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'ELECTRONICS', 'to_degree': 'WIRELESS COMMUNICATION', 'overlap_score': 0.0, 'flagged': True}]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
         <v>0</v>
       </c>
@@ -1706,24 +1710,24 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Muhammad Majid holds a PhD in Electrical Engineering from the Institute of Space Technology with a strong mark of 90.0%. His educational progression is consistent, with a stable performance trend and no significant gaps detected. However, his institutions are not ranked, which prevents his profile from being classified as strong.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06_FARMAN_ALI</t>
+          <t>38_MUHAMMAD_MUSADIQ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1732,11 +1736,11 @@
         </is>
       </c>
       <c r="C26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>declining</t>
         </is>
       </c>
       <c r="E26" t="b">
@@ -1754,24 +1758,24 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Farman Ali holds a PhD degree from Iqra National University, Peshawar, Pakistan, with a consistent progression and stable performance trend. The candidate's highest degree is a PhD, with no significant gaps detected in their educational history. The institutions attended are not ranked, which is a factor in the moderate educational strength assessment.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is declining.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07_FIZA_MURTAZA</t>
+          <t>39_MUHAMMAD_SAQIB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1788,13 +1792,9 @@
         </is>
       </c>
       <c r="E27" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>[{'from_degree': 'Computer Engineering', 'to_degree': 'Signal and Image Processing', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Signal and Image Processing', 'to_degree': 'Computer Vision, Temporal Human Action Detection', 'overlap_score': 0.0, 'flagged': True}]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
         <v>0</v>
       </c>
@@ -1806,24 +1806,24 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>The candidate, 07_FIZA_MURTAZA, holds a PhD in Computer Engineering from the University of Engineering and Technology Taxila, with a consistent progression and stable performance trend. Their highest degree is a PhD, and they have no significant educational gaps. However, the institutions they attended are not ranked highly, which contributes to their moderate educational strength.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08_TAYYABA_GULL</t>
+          <t>41_MUHAMMAD_AQEEL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>improving</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Electrical Engr', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communication', 'to_degree': 'Power Electronics', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Phy, Math, Computer', 'to_degree': 'Telecommunication Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1858,24 +1858,24 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>The candidate, 08_TAYYABA_GULL, has a PhD in Power Electronics from Iqra National University with a strong mark of 89.5%. Their educational progression is consistent, with a stable performance trend. However, there is a specialization drift from Electrical Engineering to Power Electronics, which may be a factor in the assessment. The candidate's institutions are not ranked, contributing to the moderate educational strength label.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10_MUHAMMAD_EHATISHAM</t>
+          <t>43_AMMARA_NASIM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1884,11 +1884,11 @@
         </is>
       </c>
       <c r="C29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>insufficient data</t>
         </is>
       </c>
       <c r="E29" t="b">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Computer Science', 'to_degree': 'nan', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'nan', 'to_degree': 'Signal and Image Processing', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Signal and Image Processing', 'to_degree': 'Artificial Intelligence and Pervasive Computing', 'overlap_score': 0.12, 'flagged': True}]</t>
+          <t>[{'from_degree': 'nan', 'to_degree': 'Computer Vision, AI, Deep Learning', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1910,29 +1910,29 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>The candidate has a PhD in Computer Engineering from the University of Engineering and Technology, Taxila, with a consistent specialization and strong marks throughout their academic career. They have also completed a course in Multimodal Data Processing and Machine Learning from the University of East London. The candidate's educational progression is consistent, and there are no significant gaps in their education. However, the universities they attended are not ranked, which affects their overall educational strength.</t>
+          <t>The candidate's highest qualification is PhD.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>12_SYED_TAMOORULHASSAN</t>
+          <t>02_MUHAMMAD_SHAHWAZ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C30" t="b">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Telecommunication Engineering', 'to_degree': 'Communication Systems', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'ENGINEERING', 'to_degree': 'ELECTRONICS', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1972,14 +1972,14 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>The candidate has a PhD in Communication Engineering from the University of Oulu, with a consistent progression in their educational background. They have a strong performance trend, with stable marks throughout their academic career. The candidate's specialization has drifted from Telecommunication Engineering to Communication Systems, but they have achieved high marks in their PhD program.</t>
+          <t>The candidate's highest qualification is PG. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>14_SAROSH_TAHIR</t>
+          <t>04_MUHAMMAD_FARRUKH</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre-Eng', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communication', 'to_degree': 'Next Generation Optical Networks', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Next Generation Optical Networks', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Electronic Engineering', 'to_degree': 'Digital Signal Processing', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2024,14 +2024,14 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>The candidate holds a PhD in Computer and Control Engineering from Politecnico di Torino. Their educational progression is not consistent, with specialization drift observed across different degrees. The candidate's performance trend is stable, and no significant educational gaps were detected. They have a strong foundation in engineering, with degrees in Electronics Engineering and Telecommunication and Networking.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>15_M_USMAN_ABBASI</t>
+          <t>05_MUHAMMAD_MAJID</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>improving</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E32" t="b">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Electrical Engineering', 'to_degree': 'Biomedical Signal Processing', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'PRE ENGINEERING', 'to_degree': 'ELECTRONICS', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'ELECTRONICS', 'to_degree': 'WIRELESS COMMUNICATION', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>The candidate has a PhD in Electrical Engineering from the National University of Computer and Emerging Sciences - FAST, with a consistent progression and improving performance trend. However, the specialization drift from Electrical Engineering to Biomedical Signal Processing indicates a minor drift. The candidate's academic background is solid, but the lack of ranking for most institutions attended is a factor in the assessment.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20_SYED_FASIH_ALI</t>
+          <t>06_FARMAN_ALI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2096,17 +2096,13 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>declining</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>[{'from_degree': 'Computer Engineering', 'to_degree': 'Telecommunication and Networks', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Telecommunication and Networks', 'to_degree': 'Wireless Communication', 'overlap_score': 0.0, 'flagged': True}]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
         <v>0</v>
       </c>
@@ -2123,19 +2119,19 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>The candidate, 20_SYED_FASIH_ALI, holds a PhD in Electrical Engineering from Lahore University of Management Science. Their educational progression is consistent, with a specialization that has drifted from Computer Engineering to Electrical Engineering. The candidate's performance trend is declining, which is a concern. Despite this, they have achieved strong marks in their undergraduate degree and a respectable mark in their PhD.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>21_SAMAN_FATIMA</t>
+          <t>07_FIZA_MURTAZA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2156,7 +2152,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electronics', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electronics', 'to_degree': 'E3A -M2 Integration circuits-systemes', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'E3A -M2 Integration circuits-systemes', 'to_degree': 'Microelectronics - Analog IC Design', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Computer Engineering', 'to_degree': 'Signal and Image Processing', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Signal and Image Processing', 'to_degree': 'Computer Vision, Temporal Human Action Detection', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2180,14 +2176,14 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Saman Fatima has completed her educational degrees consistently, with a highest degree of PhD from University Paris Saclay. Her performance trend has been stable, and there are no significant educational gaps detected. However, the universities for her earlier degrees are not ranked, which affects her overall educational strength.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>26_AAMINA_AKBAR</t>
+          <t>08_TAYYABA_GULL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2208,7 +2204,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Telecommunication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Telecommunication', 'to_degree': 'Wireless Communication, Convex Optimization', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Electrical Engr', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communication', 'to_degree': 'Power Electronics', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2232,14 +2228,14 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Aamina Akbar holds a PhD in Electrical Engineering with a specialization in Communication from the Institute of Space Technology. Her educational progression is consistent, and her performance trend is stable. She has a strong academic record, with high marks in her postgraduate and PhD studies, but her universities are not ranked in the top tiers, which is a factor in her moderate educational strength assessment.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>27_SHAHEER</t>
+          <t>09_SANA_FATIMA_RIZVI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2252,7 +2248,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>improving</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E36" t="b">
@@ -2260,7 +2256,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'pre engineering', 'to_degree': 'nan', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'nan', 'to_degree': 'Human Resource Management', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Human Resource Management', 'to_degree': 'POWER ELECTRONICS', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Software Engineering', 'to_degree': 'Artificial Intelligence', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Artificial Intelligence', 'to_degree': 'Machine Learning, NLP', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2279,19 +2275,19 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>The candidate has a PhD degree from University Malaysia Pahang, with a consistent progression in their educational background. However, the institutions they attended are not ranked, and there are significant specialization drifts throughout their degrees. The candidate's performance trend is improving, and there are no significant educational gaps detected.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>35_MATIULLAH_AHSAN</t>
+          <t>10_MUHAMMAD_EHATISHAM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2312,7 +2308,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'nan', 'to_degree': 'Electrical Power System, High Voltage, Artificial Intelligence', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Computer Science', 'to_degree': 'nan', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'nan', 'to_degree': 'Signal and Image Processing', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Signal and Image Processing', 'to_degree': 'Artificial Intelligence and Pervasive Computing', 'overlap_score': 0.12, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2336,14 +2332,14 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>The candidate, Matiullah Ahsan, holds a PhD in Electrical Engineering from Universiti Tun Hussein Onn Malaysia with a strong mark of 85.0%. Their educational progression is consistent, with a stable performance trend and no significant gaps detected. The candidate's specialization has drifted from an undefined area to Electrical Power System and High Voltage, with no overlap.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>36_SAMANA_BATOOL</t>
+          <t>12_SYED_TAMOORULHASSAN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2352,11 +2348,11 @@
         </is>
       </c>
       <c r="C38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>declining</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E38" t="b">
@@ -2364,7 +2360,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Artificial Intelligence in medical domain', 'to_degree': 'Computer Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Telecommunication Engineering', 'to_degree': 'Communication Systems', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2383,19 +2379,19 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>The candidate holds a PhD in Electrical Engineering from a ranked university, with a perfect score. However, their educational progression is inconsistent, and their performance trend is declining. The candidate's specialization has also drifted significantly, from Artificial Intelligence in the medical domain to Computer Engineering, with no overlap.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>38_MUHAMMAD_MUSADIQ</t>
+          <t>14_SAROSH_TAHIR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2408,13 +2404,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>declining</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>[{'from_degree': 'Pre-Eng', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communication', 'to_degree': 'Next Generation Optical Networks', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Next Generation Optical Networks', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}]</t>
+        </is>
+      </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
@@ -2431,19 +2431,19 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Muhammad Musadiq holds a PhD in Electrical Engineering from The Islamia University of Bahawalpur with a high percentage of 98.8%. However, the university is not ranked, and his performance trend shows a decline. He has a consistent specialization in Electrical Engineering throughout his degrees.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>40_ABDUR_REHMAN</t>
+          <t>21_SAMAN_FATIMA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'nan', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'nan', 'to_degree': 'Design of Electric Machines', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Electronics', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Electronics', 'to_degree': 'E3A -M2 Integration circuits-systemes', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'E3A -M2 Integration circuits-systemes', 'to_degree': 'Microelectronics - Analog IC Design', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2488,14 +2488,14 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Abdur Rehman holds a PhD in Electrical Engineering from Kunsan National University, with a consistent specialization and stable performance trend. The candidate's academic progression is consistent, with no significant gaps detected in their educational history. Abdur Rehman's highest degree is a PhD, achieved with a strong mark of 85.8%, although the universities attended are not ranked.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>41_MUHAMMAD_AQEEL</t>
+          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>improving</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E41" t="b">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Phy, Math, Computer', 'to_degree': 'Telecommunication Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Security system', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Security system', 'to_degree': 'Communications and Networks', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communications and Networks', 'to_degree': 'Intelligent Systems and Control', 'overlap_score': 0.17, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2535,19 +2535,19 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>The candidate, Muhammad Aqeel, has a PhD degree from KFUEIT with a strong academic performance trend, achieving 83.5% in their PhD program. Their educational progression is consistent, with no significant gaps detected. However, the universities they attended are not ranked, which affects their overall educational strength. The candidate's specialization has drifted from Phy, Math, Computer to Telecommunication Engineering.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>42_SAQIB_JAMIL</t>
+          <t>26_AAMINA_AKBAR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>improving</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E42" t="b">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'nan', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communication and Electronics', 'to_degree': 'Plasmonics', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'Telecommunication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Telecommunication', 'to_degree': 'Wireless Communication, Convex Optimization', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2592,14 +2592,14 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>The candidate has a PhD in Electrical Engineering from Sarhad University Peshawar, with a consistent progression and improving performance trend. Their highest degree is a PhD, and they have no significant educational gaps. The candidate's specialization has drifted over time, but they have maintained a strong academic record, with their highest marks being 87.2% in their PG degree and 85.5% in their PhD. The candidate's academic background is notable, but the lack of ranking for their institutions is a factor in their moderate educational strength.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>43_AMMARA_NASIM</t>
+          <t>35_MATIULLAH_AHSAN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2608,11 +2608,11 @@
         </is>
       </c>
       <c r="C43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>insufficient data</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'nan', 'to_degree': 'Computer Vision, AI, Deep Learning', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'nan', 'to_degree': 'Electrical Power System, High Voltage, Artificial Intelligence', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2639,19 +2639,19 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>The candidate, Ammara Nasim, holds a PhD in Computer Engineering from NUST, CEME, with a strong academic performance of 98.0%. However, their educational progression is not consistent, with a specialization drift from their initial field to Computer Vision, AI, and Deep Learning. The candidate's academic background is diverse, with degrees from multiple institutions, including NUST and UET Taxila.</t>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>33_QAMAR_ABBAS</t>
+          <t>40_ABDUR_REHMAN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2660,11 +2660,11 @@
         </is>
       </c>
       <c r="C44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>declining</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="E44" t="b">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[{'from_degree': 'Internet of thing', 'to_degree': 'Computer Engineering', 'overlap_score': 0.0, 'flagged': True}]</t>
+          <t>[{'from_degree': 'Pre-Engineering', 'to_degree': 'nan', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'nan', 'to_degree': 'Design of Electric Machines', 'overlap_score': 0.0, 'flagged': True}]</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2686,17 +2686,117 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is stable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>42_SAQIB_JAMIL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="C45" t="b">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>improving</t>
+        </is>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>[{'from_degree': 'nan', 'to_degree': 'Communication', 'overlap_score': 0.0, 'flagged': True}, {'from_degree': 'Communication and Electronics', 'to_degree': 'Plasmonics', 'overlap_score': 0.0, 'flagged': True}]</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>The candidate's highest qualification is PhD. Academic performance trend is improving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Muhammad_Dawood_Rizwan_CV</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="C46" t="b">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>insufficient data</t>
+        </is>
+      </c>
+      <c r="E46" t="b">
+        <v>0</v>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>The candidate, 33_QAMAR_ABBAS, holds a PhD from SEECS NUST with an 87.5% mark, but their educational profile shows a declining performance trend and specialization drift from Internet of Things to Computer Engineering. Their highest degree is a PhD, but the progression is not consistent. The candidate's performance has been declining over time, which raises concerns about their academic strength.</t>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>The candidate's highest qualification is UG.</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z224"/>
+  <dimension ref="A1:Z230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2882,17 +2982,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2004.0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -2926,7 +3026,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -2978,7 +3078,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2006.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -3078,7 +3178,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -3182,7 +3282,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -3194,7 +3294,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -3290,7 +3390,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -3302,7 +3402,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -3396,17 +3496,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1988.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -3444,7 +3544,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3500,17 +3600,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2003.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -3548,7 +3648,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3608,17 +3708,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2005.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -3656,7 +3756,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -3712,17 +3812,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -3760,7 +3860,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -3816,7 +3916,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -3828,7 +3928,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -3924,7 +4024,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2008.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -4028,17 +4128,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -4076,7 +4176,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -4128,7 +4228,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -4140,7 +4240,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -4232,7 +4332,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2019.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4328,17 +4428,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2023.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -4372,7 +4472,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -4428,17 +4528,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -4472,7 +4572,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -4520,17 +4620,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -4568,7 +4668,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -4620,7 +4720,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2006.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -4720,17 +4820,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2008.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -4768,7 +4868,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -4824,7 +4924,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -4924,7 +5024,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2015.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -4936,7 +5036,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -5036,7 +5136,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -5048,7 +5148,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -5148,7 +5248,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2003.0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -5248,7 +5348,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2006.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -5348,7 +5448,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -5454,7 +5554,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2015.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -5466,7 +5566,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -5566,7 +5666,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -5578,7 +5678,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -5666,17 +5766,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2004.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -5714,7 +5814,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -5766,17 +5866,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2007.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -5814,7 +5914,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -5866,7 +5966,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -5878,7 +5978,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -5974,7 +6074,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -5986,7 +6086,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -6082,7 +6182,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2019.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -6094,7 +6194,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -6186,7 +6286,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -6271,22 +6371,22 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2005.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2007.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -6324,7 +6424,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -6375,22 +6475,22 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2007.0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2009.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -6428,7 +6528,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -6483,12 +6583,12 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2009.0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2013.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -6585,12 +6685,12 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2013.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2015.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -6602,7 +6702,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -6701,12 +6801,12 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2015.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2019.0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -6718,7 +6818,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -6822,17 +6922,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -6870,7 +6970,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -6926,17 +7026,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2003.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -6974,7 +7074,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -7030,7 +7130,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2007.0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -7128,7 +7228,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2013.0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -7140,7 +7240,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -7240,7 +7340,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2023.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -7252,7 +7352,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -7352,17 +7452,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2002.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -7396,7 +7496,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -7452,17 +7552,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2004.0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
@@ -7496,7 +7596,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -7552,7 +7652,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2009.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -7564,7 +7664,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -7660,7 +7760,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -7672,7 +7772,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -7766,17 +7866,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2020.0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
@@ -7808,7 +7908,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -7864,7 +7964,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2008.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -7964,17 +8064,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -8010,7 +8110,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -8066,24 +8166,24 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -8174,7 +8274,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -8186,7 +8286,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -8282,24 +8382,24 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2020.0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -8386,7 +8486,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026.0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -8472,17 +8572,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
@@ -8516,7 +8616,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -8564,17 +8664,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2002.0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -8608,7 +8708,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -8656,7 +8756,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -8668,7 +8768,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -8760,7 +8860,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -8772,7 +8872,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -8864,7 +8964,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2016.0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -8876,7 +8976,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -8972,7 +9072,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2020.0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -8984,7 +9084,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -9072,7 +9172,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2001.0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -9172,7 +9272,7 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2003.0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -9272,17 +9372,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2007.0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -9368,7 +9468,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -9380,7 +9480,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -9470,24 +9570,24 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024.0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -9570,17 +9670,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2004.0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
@@ -9618,7 +9718,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -9670,17 +9770,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2006.0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
@@ -9718,7 +9818,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -9774,7 +9874,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -9794,7 +9894,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -9886,7 +9986,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -9906,7 +10006,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -10002,7 +10102,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022.0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -10022,7 +10122,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -10118,17 +10218,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2002.0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
@@ -10166,7 +10266,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -10222,17 +10322,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2004.0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
@@ -10270,7 +10370,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -10326,7 +10426,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2009.0</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -10424,7 +10524,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -10514,7 +10614,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -10608,7 +10708,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2002.0</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -10716,7 +10816,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2004.0</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -10820,7 +10920,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2009.0</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -10832,7 +10932,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -10932,7 +11032,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2015.0</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -10944,7 +11044,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -11044,7 +11144,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2021.0</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -11056,7 +11156,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -11150,17 +11250,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2003.0</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -11198,7 +11298,7 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
@@ -11254,17 +11354,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2005.0</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -11302,7 +11402,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
@@ -11358,7 +11458,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2009.0</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -11370,7 +11470,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -11466,7 +11566,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -11478,7 +11578,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -11574,7 +11674,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2023.0</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -11586,7 +11686,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -11686,17 +11786,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -11734,7 +11834,7 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
@@ -11794,17 +11894,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2013.0</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -11842,7 +11942,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
@@ -11898,17 +11998,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2018.0</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -11946,7 +12046,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
@@ -12006,17 +12106,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022.0</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -12050,7 +12150,7 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
@@ -12106,17 +12206,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -12150,7 +12250,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
@@ -12198,17 +12298,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2008.0</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -12242,7 +12342,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
@@ -12290,17 +12390,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -12334,7 +12434,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -12386,7 +12486,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2015.0</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -12398,7 +12498,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -12490,7 +12590,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2020.0</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -12502,7 +12602,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -12590,7 +12690,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2023.0</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -12602,7 +12702,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -12697,22 +12797,22 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2023.0</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024.0</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -12750,7 +12850,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -12802,17 +12902,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -12850,7 +12950,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
@@ -12902,17 +13002,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2002.0</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -12950,7 +13050,7 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
@@ -13006,7 +13106,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2006.0</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -13018,7 +13118,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -13110,17 +13210,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2008.0</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -13154,7 +13254,7 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
@@ -13214,7 +13314,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2021.0</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -13226,7 +13326,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -13314,17 +13414,17 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2007.0</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -13358,7 +13458,7 @@
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
@@ -13410,17 +13510,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -13454,7 +13554,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
@@ -13510,7 +13610,7 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -13522,7 +13622,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -13622,7 +13722,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2018.0</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -13634,7 +13734,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -13726,7 +13826,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -13738,7 +13838,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -13826,7 +13926,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2008.0</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -13922,7 +14022,7 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -14022,7 +14122,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -14034,7 +14134,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -14134,7 +14234,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2018.0</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -14234,7 +14334,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2023.0</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -14324,7 +14424,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2009.0</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -14424,17 +14524,17 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -14468,7 +14568,7 @@
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
@@ -14520,7 +14620,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2016.0</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -14616,17 +14716,17 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2020.0</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -14656,7 +14756,7 @@
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
@@ -14716,17 +14816,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -14760,7 +14860,7 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
@@ -14824,7 +14924,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -14932,7 +15032,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2001.0</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -15036,7 +15136,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2007.0</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -15136,24 +15236,24 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -15244,24 +15344,24 @@
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2018.0</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -15351,12 +15451,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2007.0</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2009.0</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -15463,12 +15563,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -15571,12 +15671,12 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2016.0</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -15588,7 +15688,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -15681,12 +15781,12 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2016.0</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2019.0</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -15698,7 +15798,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -15791,12 +15891,12 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2020.0</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -15808,7 +15908,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -15912,17 +16012,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2004.0</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -15960,7 +16060,7 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
@@ -16020,17 +16120,17 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2006.0</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
@@ -16068,7 +16168,7 @@
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
@@ -16124,7 +16224,7 @@
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -16226,7 +16326,7 @@
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2016.0</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -16238,7 +16338,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -16332,7 +16432,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026.0</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -16344,7 +16444,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -16436,17 +16536,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2004.0</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
@@ -16480,7 +16580,7 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
@@ -16532,17 +16632,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2006.0</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
@@ -16576,7 +16676,7 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
@@ -16632,7 +16732,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -16730,7 +16830,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2013.0</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -16742,7 +16842,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -16838,7 +16938,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -16850,7 +16950,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -16942,17 +17042,17 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1994.0</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
@@ -16986,7 +17086,7 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
@@ -17034,17 +17134,17 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1996.0</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
@@ -17078,7 +17178,7 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
@@ -17126,17 +17226,17 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2003.0</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
@@ -17170,7 +17270,7 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
@@ -17222,24 +17322,24 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2006.0</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -17318,17 +17418,17 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="M142" t="inlineStr"/>
@@ -17362,7 +17462,7 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
@@ -17414,24 +17514,24 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2021.0</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -17514,17 +17614,17 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1999.0</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
@@ -17562,7 +17662,7 @@
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
@@ -17610,17 +17710,17 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2001.0</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
@@ -17658,7 +17758,7 @@
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
@@ -17710,17 +17810,17 @@
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2006.0</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
@@ -17754,7 +17854,7 @@
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
@@ -17810,17 +17910,17 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="M147" t="inlineStr"/>
@@ -17854,7 +17954,7 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
@@ -17906,17 +18006,17 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2018.0</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="M148" t="inlineStr"/>
@@ -17950,7 +18050,7 @@
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
@@ -18006,17 +18106,17 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2009.0</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M149" t="inlineStr"/>
@@ -18050,7 +18150,7 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
@@ -18106,17 +18206,17 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M150" t="inlineStr"/>
@@ -18150,7 +18250,7 @@
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
@@ -18206,7 +18306,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2015.0</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -18218,7 +18318,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -18310,17 +18410,17 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="M152" t="inlineStr"/>
@@ -18354,7 +18454,7 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
@@ -18410,7 +18510,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024.0</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -18422,7 +18522,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -18506,7 +18606,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2004.0</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -18598,7 +18698,7 @@
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2006.0</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -18694,7 +18794,7 @@
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -18706,7 +18806,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -18806,7 +18906,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2016.0</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -18818,7 +18918,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -18910,7 +19010,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2019.0</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -18922,7 +19022,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -19006,17 +19106,17 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1999.0</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="M159" t="inlineStr"/>
@@ -19050,7 +19150,7 @@
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
@@ -19098,17 +19198,17 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2001.0</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="M160" t="inlineStr"/>
@@ -19142,7 +19242,7 @@
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
@@ -19194,17 +19294,17 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2005.0</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
@@ -19238,7 +19338,7 @@
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
@@ -19294,7 +19394,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2007.0</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -19306,7 +19406,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -19398,24 +19498,24 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -19506,24 +19606,24 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -19622,7 +19722,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -19726,7 +19826,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -20118,7 +20218,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -20218,7 +20318,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -20315,12 +20415,12 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="M172" t="inlineStr"/>
@@ -20350,7 +20450,7 @@
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
@@ -20407,12 +20507,12 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="M173" t="inlineStr"/>
@@ -20450,7 +20550,7 @@
       </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
@@ -20503,12 +20603,12 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="M174" t="inlineStr"/>
@@ -20542,7 +20642,7 @@
       </c>
       <c r="V174" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
@@ -20586,17 +20686,17 @@
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2008.0</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="M175" t="inlineStr"/>
@@ -20630,7 +20730,7 @@
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
@@ -20678,17 +20778,17 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="M176" t="inlineStr"/>
@@ -20722,7 +20822,7 @@
       </c>
       <c r="V176" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
@@ -20778,7 +20878,7 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2015.0</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -20790,7 +20890,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -20882,7 +20982,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2020.0</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -20894,7 +20994,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -20988,7 +21088,7 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024.0</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -21000,7 +21100,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -21086,7 +21186,7 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2006.0</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -21178,7 +21278,7 @@
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2009.0</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -21270,7 +21370,7 @@
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -21368,7 +21468,7 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2019.0</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -21380,7 +21480,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -21480,17 +21580,17 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="M184" t="inlineStr"/>
@@ -21528,7 +21628,7 @@
       </c>
       <c r="V184" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
@@ -21583,17 +21683,17 @@
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -21688,7 +21788,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -21788,7 +21888,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -21873,12 +21973,12 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="M188" t="inlineStr"/>
@@ -21912,7 +22012,7 @@
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
@@ -21961,12 +22061,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
@@ -22000,7 +22100,7 @@
       </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
@@ -22052,7 +22152,7 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1994.0</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -22148,7 +22248,7 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1996.0</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -22244,17 +22344,17 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2001.0</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="M192" t="inlineStr"/>
@@ -22288,7 +22388,7 @@
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
@@ -22344,7 +22444,7 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2006.0</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -22356,7 +22456,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -22452,7 +22552,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2021.0</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -22464,7 +22564,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -22572,7 +22672,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -22676,7 +22776,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -22776,7 +22876,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -22869,12 +22969,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="M198" t="inlineStr"/>
@@ -22908,7 +23008,7 @@
       </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
@@ -22961,12 +23061,12 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="M199" t="inlineStr"/>
@@ -23000,7 +23100,7 @@
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
@@ -23052,7 +23152,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -23148,7 +23248,7 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2013.0</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -23248,7 +23348,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2018.0</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -23260,7 +23360,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -23354,7 +23454,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2021.0</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -23366,7 +23466,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -23462,7 +23562,7 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -23474,7 +23574,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -23562,7 +23662,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2008.0</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -23654,7 +23754,7 @@
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -23750,7 +23850,7 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2015.0</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -23852,7 +23952,7 @@
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2019.0</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -23864,7 +23964,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -23960,7 +24060,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2023.0</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -23972,7 +24072,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -24072,17 +24172,17 @@
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="M210" t="inlineStr"/>
@@ -24120,7 +24220,7 @@
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
@@ -24180,17 +24280,17 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2013.0</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M211" t="inlineStr"/>
@@ -24228,7 +24328,7 @@
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
@@ -24284,7 +24384,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -24296,7 +24396,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -24392,7 +24492,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2020.0</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -24404,7 +24504,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -24500,7 +24600,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -24512,7 +24612,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -24600,17 +24700,17 @@
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2003.0</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="M215" t="inlineStr"/>
@@ -24644,7 +24744,7 @@
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
@@ -24692,17 +24792,17 @@
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2005.0</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="M216" t="inlineStr"/>
@@ -24736,7 +24836,7 @@
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
@@ -24792,7 +24892,7 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -24804,7 +24904,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -24900,7 +25000,7 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2015.0</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -24912,7 +25012,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -25008,7 +25108,7 @@
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2023.0</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -25020,7 +25120,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -25108,7 +25208,7 @@
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2008.0</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -25200,7 +25300,7 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2008.0</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -25296,7 +25396,7 @@
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -25308,7 +25408,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -25400,7 +25500,7 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2016.0</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -25412,7 +25512,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -25512,7 +25612,7 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -25524,7 +25624,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -25578,6 +25678,604 @@
       <c r="Y224" t="inlineStr"/>
       <c r="Z224" t="n">
         <v>61.53846153846154</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>09_SANA_FATIMA_RIZVI</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>HSSC</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>FSc</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Pre Engineering</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>BISE Rawalpindi</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>2008.0</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr"/>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>HSSC</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="X225" t="n">
+        <v>71</v>
+      </c>
+      <c r="Y225" t="inlineStr"/>
+      <c r="Z225" t="n">
+        <v>33.33333333333334</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>09_SANA_FATIMA_RIZVI</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>University of Engineering &amp; Technology, Taxila</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>2012.0</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr"/>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>nan/nan</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>cgpa_nan</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr"/>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>University of Engineering and Technology Taxila</t>
+        </is>
+      </c>
+      <c r="Z226" t="n">
+        <v>95.55555555555556</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>09_SANA_FATIMA_RIZVI</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>University of Engineering &amp; Technology, Taxila</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>2016.0</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr"/>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>3.65/4.0</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>cgpa_4</t>
+        </is>
+      </c>
+      <c r="X227" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>University of Engineering and Technology Taxila</t>
+        </is>
+      </c>
+      <c r="Z227" t="n">
+        <v>95.55555555555556</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>09_SANA_FATIMA_RIZVI</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Machine Learning, NLP</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Beihang University</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>2023.0</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr"/>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>3.82/4.0</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>cgpa_4</t>
+        </is>
+      </c>
+      <c r="X228" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>Mehran University of Engineering and Technology</t>
+        </is>
+      </c>
+      <c r="Z228" t="n">
+        <v>85.71428571428572</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Muhammad_Dawood_Rizwan_CV</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Bachelor of Information Technology</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Punjab University College of Information Technology (PUCIT)</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>2020.0</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>2024.0</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Constituent college of the University of the Punjab; not ranked separately in global rankings.</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>nan/nan</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>cgpa_nan</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr"/>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>Sarhad University of Science and Information Technology</t>
+        </is>
+      </c>
+      <c r="Z229" t="n">
+        <v>73.21428571428572</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Muhammad_Dawood_Rizwan_CV</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Fellowship</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>RPTU TU Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>2025.0</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>2025.0</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>Not Ranked</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>RPTU is the merged entity of TU Kaiserslautern and TU Ludwigshafen; rankings often still list the institution as TU Kaiserslautern.</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>nan/nan</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>cgpa_nan</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr"/>
+      <c r="Y230" t="inlineStr"/>
+      <c r="Z230" t="n">
+        <v>45.71428571428572</v>
       </c>
     </row>
   </sheetData>
